--- a/99_tips/生産対策交付金_交付額整理表.xlsx
+++ b/99_tips/生産対策交付金_交付額整理表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\r_analysis\miyagi-agricultural-recovery\miyagi-agricultural-recovery\99_tips\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCC73AA7-7C69-4CFF-A56C-75A0A97879E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26C95D7C-C5D6-4C42-954E-CA546C8C9F77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2660" yWindow="2660" windowWidth="28770" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="114">
   <si>
     <t>名取市</t>
     <rPh sb="0" eb="3">
@@ -369,6 +369,364 @@
   </si>
   <si>
     <t xml:space="preserve">グリーン機械利用組合 </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>耕谷アグリサービス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>下増田村</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>北目転作組合</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>名取市花卉生産組合</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>閖上町</t>
+    <rPh sb="0" eb="2">
+      <t>ユリアゲ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>マチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>美田園ファーム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>名取グリーンファーマーズ出荷組合</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>北釜耕人会</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>増田町</t>
+    <rPh sb="0" eb="2">
+      <t>マスダ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>マチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>岩沼市</t>
+    <rPh sb="0" eb="3">
+      <t>イワヌマシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>やさい工房八巻</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>玉浦村</t>
+    <rPh sb="0" eb="2">
+      <t>タマウラ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ムラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>岩沼園芸組合</t>
+    <rPh sb="0" eb="2">
+      <t>イワヌマ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>エンゲイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>クミアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>玉浦村</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>玉浦中部地区生産組合</t>
+    <rPh sb="0" eb="2">
+      <t>タマウラ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>チュウブ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>チク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>セイサン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>クミアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>山元町</t>
+    <rPh sb="0" eb="2">
+      <t>ヤマモト</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>マチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>山元町アグリカルチャー</t>
+    <rPh sb="0" eb="3">
+      <t>ヤマモトチョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>石巻市</t>
+    <rPh sb="0" eb="3">
+      <t>イシノマキシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゆいっこ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>橋浦村</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>いちごランド石巻</t>
+    <rPh sb="6" eb="8">
+      <t>イシノマキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>蛇田村</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>東松島市</t>
+    <rPh sb="0" eb="4">
+      <t>ヒガシマツシマシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サンエイト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>小野村</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アグリードなるせ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>野蒜村</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>絆組合</t>
+    <rPh sb="0" eb="1">
+      <t>キズナ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>クミアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>荒浜アグリパートナーズ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（七郷）</t>
+  </si>
+  <si>
+    <t>e-farm仙台</t>
+  </si>
+  <si>
+    <t>枝豆元気クラブ</t>
+  </si>
+  <si>
+    <t>井土生産組合</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（六郷）</t>
+  </si>
+  <si>
+    <t>クローバーズファーム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>せんだいあらはま</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>笹屋敷護穀組合</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>三本塚機械利用組合</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>下荒井カントリー</t>
+    <rPh sb="0" eb="3">
+      <t>シモアライ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>六郷南部実践組合</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>福鶴ファーム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>藤田生産組合</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>二木営農実践組合</t>
+  </si>
+  <si>
+    <t>四ツ谷作業組合</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>三神会</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>相野釜ハウス園芸組合</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ぱるファーム大曲</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>矢本町</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>赤井村</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>イグナルファーム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>三本塚営農実践組合</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>なつき農園</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>絆ファーム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フィールドファーム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>トータスファーム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>宮城リスタ大川</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>大川村</t>
+    <rPh sb="0" eb="3">
+      <t>オオカワムラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>葱掘取機利用組合</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>下飯田中機械利用組合</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>野菜のキセキ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>玉浦南部生産組合</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>林ライス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>めぐいーと</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>創菜組合</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>名取北釜ファーム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>長谷釜生産組合</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>寺島生産組合</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>いそはま</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>坂元村</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>やまもとファームみらい野</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>山下村</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パスカファーム立沼</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -412,11 +770,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -697,15 +1059,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V35"/>
+  <dimension ref="A1:V74"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="10.4140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.08203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.1640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="22.58203125" style="1" customWidth="1"/>
-    <col min="6" max="14" width="22.58203125" customWidth="1"/>
+    <col min="5" max="5" width="22.58203125" style="2" customWidth="1"/>
+    <col min="6" max="13" width="22.58203125" style="3" customWidth="1"/>
+    <col min="14" max="14" width="22.58203125" customWidth="1"/>
     <col min="15" max="22" width="18.6640625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -722,31 +1085,31 @@
       <c r="D1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>14</v>
       </c>
       <c r="N1" s="1" t="s">
@@ -773,7 +1136,7 @@
       <c r="D2" s="1">
         <v>1</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="2">
         <v>14034000</v>
       </c>
     </row>
@@ -790,8 +1153,11 @@
       <c r="D3" s="1">
         <v>1</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="2">
         <v>15383000</v>
+      </c>
+      <c r="G3" s="3">
+        <v>8325000</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -807,7 +1173,7 @@
       <c r="D4" s="1">
         <v>1</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="2">
         <v>9851000</v>
       </c>
     </row>
@@ -835,8 +1201,11 @@
       <c r="D6" s="1">
         <v>1</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="2">
         <v>7450000</v>
+      </c>
+      <c r="G6" s="3">
+        <v>9818000</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -852,8 +1221,11 @@
       <c r="D7" s="1">
         <v>2</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="2">
         <v>5800000</v>
+      </c>
+      <c r="G7" s="3">
+        <v>2608000</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -869,8 +1241,11 @@
       <c r="D8" s="1">
         <v>1</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="2">
         <v>8075000</v>
+      </c>
+      <c r="H8" s="3">
+        <v>1105000</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -886,8 +1261,11 @@
       <c r="D9" s="1">
         <v>2</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" s="2">
         <v>5800000</v>
+      </c>
+      <c r="G9" s="3">
+        <v>7102000</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -903,7 +1281,7 @@
       <c r="D10" s="1">
         <v>1</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10" s="2">
         <v>10690000</v>
       </c>
     </row>
@@ -920,8 +1298,11 @@
       <c r="D11" s="1">
         <v>2</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11" s="2">
         <v>11693000</v>
+      </c>
+      <c r="G11" s="3">
+        <v>3219000</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -937,8 +1318,11 @@
       <c r="D12" s="1">
         <v>2</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12" s="2">
         <v>8325000</v>
+      </c>
+      <c r="G12" s="3">
+        <v>3210000</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -954,8 +1338,11 @@
       <c r="D13" s="1">
         <v>1</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13" s="2">
         <v>10125000</v>
+      </c>
+      <c r="H13" s="3">
+        <v>712000</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -971,7 +1358,7 @@
       <c r="D14" s="1">
         <v>1</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E14" s="2">
         <v>19290000</v>
       </c>
     </row>
@@ -988,8 +1375,11 @@
       <c r="D15" s="1">
         <v>2</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E15" s="2">
         <v>14939000</v>
+      </c>
+      <c r="G15" s="3">
+        <v>15393000</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -1005,11 +1395,14 @@
       <c r="D16" s="1">
         <v>1</v>
       </c>
-      <c r="E16" s="1">
+      <c r="E16" s="2">
         <v>6900000</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="G16" s="3">
+        <v>2329000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" t="s">
         <v>1</v>
       </c>
@@ -1022,11 +1415,14 @@
       <c r="D17" s="1">
         <v>2</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E17" s="2">
         <v>3250000</v>
       </c>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="G17" s="3">
+        <v>7667000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" t="s">
         <v>1</v>
       </c>
@@ -1039,11 +1435,11 @@
       <c r="D18" s="1">
         <v>2</v>
       </c>
-      <c r="E18" s="1">
+      <c r="E18" s="2">
         <v>4380000</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:9">
       <c r="A19" t="s">
         <v>1</v>
       </c>
@@ -1056,11 +1452,14 @@
       <c r="D19" s="1">
         <v>1</v>
       </c>
-      <c r="E19" s="1">
+      <c r="E19" s="2">
         <v>8860000</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
+      <c r="G19" s="3">
+        <v>2984000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" t="s">
         <v>1</v>
       </c>
@@ -1071,7 +1470,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:9">
       <c r="A21" t="s">
         <v>1</v>
       </c>
@@ -1084,11 +1483,11 @@
       <c r="D21" s="1">
         <v>2</v>
       </c>
-      <c r="E21" s="1">
+      <c r="E21" s="2">
         <v>2750000</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:9">
       <c r="A22" t="s">
         <v>1</v>
       </c>
@@ -1099,29 +1498,879 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:9">
       <c r="A23" t="s">
+        <v>1</v>
+      </c>
+      <c r="B23" t="s">
+        <v>69</v>
+      </c>
+      <c r="D23" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" t="s">
+        <v>1</v>
+      </c>
+      <c r="B24" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D24" s="1">
+        <v>1</v>
+      </c>
+      <c r="G24" s="2">
+        <v>3368000</v>
+      </c>
+      <c r="H24" s="3">
+        <v>1093000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" t="s">
+        <v>1</v>
+      </c>
+      <c r="B25" t="s">
+        <v>72</v>
+      </c>
+      <c r="D25" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B26" t="s">
+        <v>73</v>
+      </c>
+      <c r="D26" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" t="s">
+        <v>1</v>
+      </c>
+      <c r="B27" t="s">
+        <v>74</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
+      <c r="G27" s="3">
+        <v>4013000</v>
+      </c>
+      <c r="H27" s="3">
+        <v>4995000</v>
+      </c>
+      <c r="I27" s="3">
+        <v>8887000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" t="s">
+        <v>1</v>
+      </c>
+      <c r="B28" t="s">
+        <v>76</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
+      <c r="G28" s="3">
+        <v>10119000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" t="s">
+        <v>1</v>
+      </c>
+      <c r="B29" t="s">
+        <v>77</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
+      <c r="G29" s="3">
+        <v>7569000</v>
+      </c>
+      <c r="H29" s="3">
+        <v>1432000</v>
+      </c>
+      <c r="I29" s="3">
+        <f>3220000+1426000</f>
+        <v>4646000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" t="s">
+        <v>1</v>
+      </c>
+      <c r="B30" t="s">
+        <v>78</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D30" s="1">
+        <v>1</v>
+      </c>
+      <c r="G30" s="3">
+        <v>3738000</v>
+      </c>
+      <c r="H30" s="3">
+        <v>2083000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B31" t="s">
+        <v>79</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" s="1">
+        <v>1</v>
+      </c>
+      <c r="G31" s="3">
+        <v>7891000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" t="s">
+        <v>1</v>
+      </c>
+      <c r="B32" t="s">
+        <v>80</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D32" s="1">
+        <v>2</v>
+      </c>
+      <c r="G32" s="3">
+        <v>3163000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" t="s">
+        <v>1</v>
+      </c>
+      <c r="B33" t="s">
+        <v>81</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D33" s="1">
+        <v>1</v>
+      </c>
+      <c r="G33" s="3">
+        <v>4893000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" t="s">
+        <v>1</v>
+      </c>
+      <c r="B34" t="s">
+        <v>82</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D34" s="1">
+        <v>1</v>
+      </c>
+      <c r="G34" s="3">
+        <v>12165000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" t="s">
+        <v>1</v>
+      </c>
+      <c r="B35" t="s">
+        <v>83</v>
+      </c>
+      <c r="D35" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" t="s">
+        <v>1</v>
+      </c>
+      <c r="B36" t="s">
+        <v>84</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D36" s="1">
+        <v>2</v>
+      </c>
+      <c r="G36" s="3">
+        <v>3923000</v>
+      </c>
+      <c r="H36" s="3">
+        <v>155000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B37" t="s">
+        <v>85</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D37" s="1">
+        <v>1</v>
+      </c>
+      <c r="G37" s="3">
+        <v>1201000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" t="s">
+        <v>1</v>
+      </c>
+      <c r="B38" t="s">
+        <v>86</v>
+      </c>
+      <c r="D38" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" t="s">
+        <v>1</v>
+      </c>
+      <c r="B39" t="s">
+        <v>92</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D39" s="1">
+        <v>2</v>
+      </c>
+      <c r="G39" s="3">
+        <v>1260000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" t="s">
+        <v>1</v>
+      </c>
+      <c r="B40" t="s">
+        <v>93</v>
+      </c>
+      <c r="D40" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" t="s">
+        <v>1</v>
+      </c>
+      <c r="B41" t="s">
+        <v>94</v>
+      </c>
+      <c r="D41" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" t="s">
+        <v>1</v>
+      </c>
+      <c r="B42" t="s">
+        <v>95</v>
+      </c>
+      <c r="D42" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" t="s">
+        <v>1</v>
+      </c>
+      <c r="B43" t="s">
+        <v>96</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D43" s="1">
+        <v>1</v>
+      </c>
+      <c r="G43" s="3">
+        <v>13399000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" t="s">
+        <v>1</v>
+      </c>
+      <c r="B44" t="s">
+        <v>100</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D44" s="1">
+        <v>2</v>
+      </c>
+      <c r="G44" s="3">
+        <v>221000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" t="s">
+        <v>1</v>
+      </c>
+      <c r="B45" t="s">
+        <v>105</v>
+      </c>
+      <c r="D45" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="6:22">
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
-      <c r="L35" s="1"/>
-      <c r="M35" s="1"/>
-      <c r="N35" s="1"/>
-      <c r="O35" s="1"/>
-      <c r="P35" s="1"/>
-      <c r="Q35" s="1"/>
-      <c r="R35" s="1"/>
-      <c r="S35" s="1"/>
-      <c r="T35" s="1"/>
-      <c r="U35" s="1"/>
-      <c r="V35" s="1"/>
+      <c r="B46" t="s">
+        <v>42</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D46" s="1">
+        <v>1</v>
+      </c>
+      <c r="E46" s="2">
+        <v>11875000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" t="s">
+        <v>0</v>
+      </c>
+      <c r="B47" t="s">
+        <v>44</v>
+      </c>
+      <c r="D47" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" t="s">
+        <v>0</v>
+      </c>
+      <c r="B48" t="s">
+        <v>45</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D48" s="1">
+        <v>1</v>
+      </c>
+      <c r="E48" s="2">
+        <v>34036000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11">
+      <c r="A49" t="s">
+        <v>0</v>
+      </c>
+      <c r="B49" t="s">
+        <v>47</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D49" s="1">
+        <v>1</v>
+      </c>
+      <c r="E49" s="2">
+        <v>13320000</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50" t="s">
+        <v>0</v>
+      </c>
+      <c r="B50" t="s">
+        <v>48</v>
+      </c>
+      <c r="D50" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11">
+      <c r="A51" t="s">
+        <v>0</v>
+      </c>
+      <c r="B51" t="s">
+        <v>49</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D51" s="1">
+        <v>1</v>
+      </c>
+      <c r="E51" s="2">
+        <v>1978000</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11">
+      <c r="A52" t="s">
+        <v>0</v>
+      </c>
+      <c r="B52" t="s">
+        <v>106</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D52" s="1">
+        <v>1</v>
+      </c>
+      <c r="I52" s="3">
+        <v>5668000</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11">
+      <c r="A53" t="s">
+        <v>51</v>
+      </c>
+      <c r="B53" t="s">
+        <v>52</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D53" s="1">
+        <v>1</v>
+      </c>
+      <c r="E53" s="2">
+        <v>43877000</v>
+      </c>
+      <c r="I53" s="3">
+        <v>27975000</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11">
+      <c r="A54" t="s">
+        <v>51</v>
+      </c>
+      <c r="B54" t="s">
+        <v>54</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D54" s="1">
+        <v>1</v>
+      </c>
+      <c r="E54" s="2">
+        <v>12606000</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11">
+      <c r="A55" t="s">
+        <v>51</v>
+      </c>
+      <c r="B55" t="s">
+        <v>56</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D55" s="1">
+        <v>1</v>
+      </c>
+      <c r="E55" s="2">
+        <v>3102000</v>
+      </c>
+      <c r="H55" s="3">
+        <v>24400000</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11">
+      <c r="A56" t="s">
+        <v>51</v>
+      </c>
+      <c r="B56" t="s">
+        <v>87</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D56" s="1">
+        <v>1</v>
+      </c>
+      <c r="G56" s="3">
+        <v>1050000</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11">
+      <c r="A57" t="s">
+        <v>51</v>
+      </c>
+      <c r="B57" t="s">
+        <v>101</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D57" s="1">
+        <v>1</v>
+      </c>
+      <c r="G57" s="3">
+        <v>26900000</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11">
+      <c r="A58" t="s">
+        <v>51</v>
+      </c>
+      <c r="B58" t="s">
+        <v>102</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D58" s="1">
+        <v>1</v>
+      </c>
+      <c r="H58" s="3">
+        <v>350000</v>
+      </c>
+      <c r="I58" s="3">
+        <v>850000</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11">
+      <c r="A59" t="s">
+        <v>51</v>
+      </c>
+      <c r="B59" t="s">
+        <v>103</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D59" s="1">
+        <v>1</v>
+      </c>
+      <c r="H59" s="3">
+        <v>5250000</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11">
+      <c r="A60" t="s">
+        <v>51</v>
+      </c>
+      <c r="B60" t="s">
+        <v>107</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D60" s="1">
+        <v>1</v>
+      </c>
+      <c r="I60" s="3">
+        <v>2650000</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11">
+      <c r="A61" t="s">
+        <v>51</v>
+      </c>
+      <c r="B61" t="s">
+        <v>108</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D61" s="1">
+        <v>1</v>
+      </c>
+      <c r="I61" s="3">
+        <v>3490000</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11">
+      <c r="A62" t="s">
+        <v>57</v>
+      </c>
+      <c r="B62" t="s">
+        <v>58</v>
+      </c>
+      <c r="D62" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11">
+      <c r="A63" t="s">
+        <v>57</v>
+      </c>
+      <c r="B63" t="s">
+        <v>109</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D63" s="1">
+        <v>1</v>
+      </c>
+      <c r="I63" s="3">
+        <v>2139000</v>
+      </c>
+      <c r="J63" s="3">
+        <v>306000</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11">
+      <c r="A64" t="s">
+        <v>57</v>
+      </c>
+      <c r="B64" t="s">
+        <v>111</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D64" s="1">
+        <v>1</v>
+      </c>
+      <c r="I64" s="3">
+        <v>25741000</v>
+      </c>
+      <c r="J64" s="3">
+        <v>914000</v>
+      </c>
+      <c r="K64" s="3">
+        <v>1618000</v>
+      </c>
+    </row>
+    <row r="65" spans="1:22">
+      <c r="A65" t="s">
+        <v>59</v>
+      </c>
+      <c r="B65" t="s">
+        <v>60</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D65" s="1">
+        <v>1</v>
+      </c>
+      <c r="E65" s="2">
+        <v>12245000</v>
+      </c>
+    </row>
+    <row r="66" spans="1:22">
+      <c r="A66" t="s">
+        <v>59</v>
+      </c>
+      <c r="B66" t="s">
+        <v>62</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D66" s="1">
+        <v>1</v>
+      </c>
+      <c r="E66" s="2">
+        <v>8250000</v>
+      </c>
+    </row>
+    <row r="67" spans="1:22">
+      <c r="A67" t="s">
+        <v>59</v>
+      </c>
+      <c r="B67" t="s">
+        <v>97</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D67" s="1">
+        <v>1</v>
+      </c>
+      <c r="G67" s="3">
+        <v>2153000</v>
+      </c>
+    </row>
+    <row r="68" spans="1:22">
+      <c r="A68" t="s">
+        <v>64</v>
+      </c>
+      <c r="B68" t="s">
+        <v>65</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D68" s="1">
+        <v>1</v>
+      </c>
+      <c r="E68" s="2">
+        <v>22920000</v>
+      </c>
+      <c r="F68" s="2"/>
+      <c r="G68" s="2">
+        <v>3677000</v>
+      </c>
+      <c r="H68" s="2"/>
+      <c r="I68" s="2"/>
+      <c r="J68" s="2"/>
+      <c r="K68" s="2"/>
+      <c r="L68" s="2"/>
+      <c r="M68" s="2"/>
+      <c r="N68" s="1"/>
+      <c r="O68" s="1"/>
+      <c r="P68" s="1"/>
+      <c r="Q68" s="1"/>
+      <c r="R68" s="1"/>
+      <c r="S68" s="1"/>
+      <c r="T68" s="1"/>
+      <c r="U68" s="1"/>
+      <c r="V68" s="1"/>
+    </row>
+    <row r="69" spans="1:22">
+      <c r="A69" t="s">
+        <v>64</v>
+      </c>
+      <c r="B69" t="s">
+        <v>67</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D69" s="1">
+        <v>1</v>
+      </c>
+      <c r="E69" s="2">
+        <v>27339000</v>
+      </c>
+      <c r="G69" s="3">
+        <v>8656000</v>
+      </c>
+    </row>
+    <row r="70" spans="1:22">
+      <c r="A70" t="s">
+        <v>64</v>
+      </c>
+      <c r="B70" t="s">
+        <v>88</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D70" s="1">
+        <v>1</v>
+      </c>
+      <c r="G70" s="3">
+        <v>1959000</v>
+      </c>
+      <c r="I70" s="3">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="71" spans="1:22">
+      <c r="A71" t="s">
+        <v>64</v>
+      </c>
+      <c r="B71" t="s">
+        <v>91</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D71" s="1">
+        <v>1</v>
+      </c>
+      <c r="G71" s="3">
+        <v>2100000</v>
+      </c>
+    </row>
+    <row r="72" spans="1:22">
+      <c r="A72" t="s">
+        <v>64</v>
+      </c>
+      <c r="B72" t="s">
+        <v>99</v>
+      </c>
+      <c r="D72" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:22">
+      <c r="A73" t="s">
+        <v>64</v>
+      </c>
+      <c r="B73" t="s">
+        <v>104</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D73" s="1">
+        <v>1</v>
+      </c>
+      <c r="H73" s="3">
+        <v>5042000</v>
+      </c>
+      <c r="I73" s="3">
+        <v>2639000</v>
+      </c>
+    </row>
+    <row r="74" spans="1:22">
+      <c r="A74" t="s">
+        <v>64</v>
+      </c>
+      <c r="B74" t="s">
+        <v>113</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D74" s="1">
+        <v>1</v>
+      </c>
+      <c r="I74" s="3">
+        <v>471000</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
